--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post DFS_HRM-2031-0220/Panel-28/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post DFS_HRM-2031-0220/Panel-28/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.41164</v>
+        <v>17.67913</v>
       </c>
       <c r="D2" t="n">
-        <v>17.30712</v>
+        <v>17.30626</v>
       </c>
       <c r="E2" t="n">
-        <v>17.38968</v>
+        <v>17.59394</v>
       </c>
       <c r="F2" t="n">
-        <v>44.27855</v>
+        <v>44.15014</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05335</v>
+        <v>0.05286</v>
       </c>
       <c r="H2" t="n">
-        <v>1.88447</v>
+        <v>1.97144</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.89267</v>
+        <v>17.80452</v>
       </c>
       <c r="D3" t="n">
-        <v>17.29233</v>
+        <v>17.06437</v>
       </c>
       <c r="E3" t="n">
-        <v>17.46572</v>
+        <v>17.70142</v>
       </c>
       <c r="F3" t="n">
-        <v>43.86914</v>
+        <v>44.81141</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0527</v>
+        <v>0.05328</v>
       </c>
       <c r="H3" t="n">
-        <v>1.92353</v>
+        <v>1.93146</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.56931</v>
+        <v>17.79943</v>
       </c>
       <c r="D4" t="n">
-        <v>17.35813</v>
+        <v>17.35405</v>
       </c>
       <c r="E4" t="n">
-        <v>17.41099</v>
+        <v>17.58208</v>
       </c>
       <c r="F4" t="n">
-        <v>45.17558</v>
+        <v>43.9137</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05304</v>
+        <v>0.05367</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8928</v>
+        <v>1.93246</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.59843</v>
+        <v>17.44785</v>
       </c>
       <c r="D6" t="n">
-        <v>16.84249</v>
+        <v>16.88327</v>
       </c>
       <c r="E6" t="n">
-        <v>17.53448</v>
+        <v>17.295</v>
       </c>
       <c r="F6" t="n">
-        <v>22.72999</v>
+        <v>22.79761</v>
       </c>
       <c r="G6" t="n">
-        <v>35.68058</v>
+        <v>35.64766</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.06302</v>
+        <v>17.48736</v>
       </c>
       <c r="D7" t="n">
-        <v>17.06702</v>
+        <v>16.79091</v>
       </c>
       <c r="E7" t="n">
-        <v>16.86569</v>
+        <v>16.897</v>
       </c>
       <c r="F7" t="n">
-        <v>22.64674</v>
+        <v>21.82862</v>
       </c>
       <c r="G7" t="n">
-        <v>36.0451</v>
+        <v>36.30141</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.3869</v>
+        <v>17.61615</v>
       </c>
       <c r="D8" t="n">
-        <v>16.60453</v>
+        <v>17.01381</v>
       </c>
       <c r="E8" t="n">
-        <v>17.18842</v>
+        <v>17.10039</v>
       </c>
       <c r="F8" t="n">
-        <v>22.84618</v>
+        <v>22.88577</v>
       </c>
       <c r="G8" t="n">
-        <v>36.29029</v>
+        <v>36.21095</v>
       </c>
     </row>
   </sheetData>
